--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/AUSTRALIA-MATARANKA_Datenbank/before_conversion_australia_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/AUSTRALIA-MATARANKA_Datenbank/before_conversion_australia_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="426">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Daly</t>
@@ -1652,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD85"/>
+  <dimension ref="A1:AE85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1681,9 +1684,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1774,13 +1778,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>-14.444255748</v>
@@ -1789,36 +1796,36 @@
         <v>132.285449884</v>
       </c>
       <c r="N2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="S2">
         <v>524.74448</v>
       </c>
       <c r="U2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AD2">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>-14.54653</v>
@@ -1827,36 +1834,36 @@
         <v>132.395</v>
       </c>
       <c r="N3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S3">
         <v>445.42264</v>
       </c>
       <c r="U3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AD3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4">
         <v>-14.710453</v>
@@ -1865,36 +1872,36 @@
         <v>132.059519</v>
       </c>
       <c r="N4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S4">
         <v>402.71088</v>
       </c>
       <c r="U4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AD4">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>-14.710453</v>
@@ -1903,36 +1910,36 @@
         <v>132.059519</v>
       </c>
       <c r="N5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S5">
         <v>341.69408</v>
       </c>
       <c r="U5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AD5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>-14.57557</v>
@@ -1941,36 +1948,36 @@
         <v>132.4713</v>
       </c>
       <c r="N6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S6">
         <v>512.5411200000001</v>
       </c>
       <c r="U6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AD6">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>-14.48369</v>
@@ -1979,36 +1986,36 @@
         <v>132.247</v>
       </c>
       <c r="N7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S7">
         <v>482.03272</v>
       </c>
       <c r="U7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AD7">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>-14.457564171</v>
@@ -2017,36 +2024,36 @@
         <v>132.2414534</v>
       </c>
       <c r="N8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="S8">
         <v>366.1008000000001</v>
       </c>
       <c r="U8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AD8">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>-14.5679</v>
@@ -2055,36 +2062,36 @@
         <v>132.5053</v>
       </c>
       <c r="N9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S9">
         <v>408.81256</v>
       </c>
       <c r="U9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AD9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>-14.454347743</v>
@@ -2093,36 +2100,36 @@
         <v>132.213009476</v>
       </c>
       <c r="N10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="S10">
         <v>421.0159200000001</v>
       </c>
       <c r="U10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AD10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>-14.41105</v>
@@ -2131,36 +2138,36 @@
         <v>132.2043</v>
       </c>
       <c r="N11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="R11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S11">
         <v>366.1008000000001</v>
       </c>
       <c r="U11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>-14.50392779</v>
@@ -2169,36 +2176,36 @@
         <v>132.295794198</v>
       </c>
       <c r="N12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S12">
         <v>463.72768</v>
       </c>
       <c r="U12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AD12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>-14.50392779</v>
@@ -2207,36 +2214,36 @@
         <v>132.295794198</v>
       </c>
       <c r="N13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S13">
         <v>421.0159200000001</v>
       </c>
       <c r="U13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AD13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14">
         <v>-14.488736</v>
@@ -2245,36 +2252,36 @@
         <v>132.255447</v>
       </c>
       <c r="N14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="R14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="S14">
         <v>402.71088</v>
       </c>
       <c r="U14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AD14">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>-14.383915</v>
@@ -2283,36 +2290,36 @@
         <v>132.150887</v>
       </c>
       <c r="N15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S15">
         <v>482.03272</v>
       </c>
       <c r="U15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <v>-14.47812</v>
@@ -2321,25 +2328,25 @@
         <v>132.2691</v>
       </c>
       <c r="N16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S16">
         <v>286.77896</v>
       </c>
       <c r="U16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AD16">
         <v>9</v>
@@ -2347,10 +2354,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>-14.45767</v>
@@ -2359,25 +2366,25 @@
         <v>132.2564</v>
       </c>
       <c r="N17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S17">
         <v>451.5243200000001</v>
       </c>
       <c r="U17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AD17">
         <v>9</v>
@@ -2385,10 +2392,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>-14.47144</v>
@@ -2397,25 +2404,25 @@
         <v>132.235</v>
       </c>
       <c r="N18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S18">
         <v>408.81256</v>
       </c>
       <c r="U18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD18">
         <v>9</v>
@@ -2423,10 +2430,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>-14.47399</v>
@@ -2435,25 +2442,25 @@
         <v>132.2368</v>
       </c>
       <c r="N19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="R19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S19">
         <v>408.81256</v>
       </c>
       <c r="U19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD19">
         <v>9</v>
@@ -2461,10 +2468,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>-14.44705</v>
@@ -2473,25 +2480,25 @@
         <v>132.2492</v>
       </c>
       <c r="N20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S20">
         <v>451.5243200000001</v>
       </c>
       <c r="U20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AD20">
         <v>9</v>
@@ -2499,10 +2506,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>-14.4563</v>
@@ -2511,25 +2518,25 @@
         <v>132.261</v>
       </c>
       <c r="N21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q21" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="R21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S21">
         <v>585.7612800000001</v>
       </c>
       <c r="U21" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AD21">
         <v>9</v>
@@ -2537,10 +2544,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22">
         <v>-14.48668</v>
@@ -2549,25 +2556,25 @@
         <v>132.2505</v>
       </c>
       <c r="N22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R22" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S22">
         <v>463.72768</v>
       </c>
       <c r="U22" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AD22">
         <v>9</v>
@@ -2575,10 +2582,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <v>-14.4449</v>
@@ -2587,25 +2594,25 @@
         <v>132.2504</v>
       </c>
       <c r="N23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P23" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R23" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S23">
         <v>500.33776</v>
       </c>
       <c r="U23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AD23">
         <v>9</v>
@@ -2613,10 +2620,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24">
         <v>-14.45287</v>
@@ -2625,25 +2632,25 @@
         <v>132.2453</v>
       </c>
       <c r="N24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R24" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S24">
         <v>451.5243200000001</v>
       </c>
       <c r="U24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AD24">
         <v>9</v>
@@ -2651,10 +2658,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25">
         <v>-14.46378</v>
@@ -2663,25 +2670,25 @@
         <v>132.2365</v>
       </c>
       <c r="N25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q25" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R25" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S25">
         <v>378.30416</v>
       </c>
       <c r="U25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD25">
         <v>9</v>
@@ -2689,10 +2696,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26">
         <v>-14.48027</v>
@@ -2701,25 +2708,25 @@
         <v>132.2401</v>
       </c>
       <c r="N26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q26" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="R26" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S26">
         <v>482.03272</v>
       </c>
       <c r="U26" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AD26">
         <v>9</v>
@@ -2727,10 +2734,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27">
         <v>-14.46632</v>
@@ -2739,25 +2746,25 @@
         <v>132.2837</v>
       </c>
       <c r="N27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O27" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R27" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="S27">
         <v>488.1344</v>
       </c>
       <c r="U27" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD27">
         <v>9</v>
@@ -2765,10 +2772,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28">
         <v>-14.49033</v>
@@ -2777,25 +2784,25 @@
         <v>132.2358</v>
       </c>
       <c r="N28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R28" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S28">
         <v>457.626</v>
       </c>
       <c r="U28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AD28">
         <v>9</v>
@@ -2803,10 +2810,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>-14.46596</v>
@@ -2815,25 +2822,25 @@
         <v>132.284</v>
       </c>
       <c r="N29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q29" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S29">
         <v>414.91424</v>
       </c>
       <c r="U29" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AD29">
         <v>9</v>
@@ -2841,10 +2848,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30">
         <v>-14.539374</v>
@@ -2853,25 +2860,25 @@
         <v>132.174356</v>
       </c>
       <c r="N30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S30">
         <v>335.5924</v>
       </c>
       <c r="U30" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AD30">
         <v>9</v>
@@ -2879,10 +2886,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31">
         <v>-14.46924</v>
@@ -2891,25 +2898,25 @@
         <v>132.1967</v>
       </c>
       <c r="N31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R31" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="S31">
         <v>390.5075200000001</v>
       </c>
       <c r="U31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD31">
         <v>9</v>
@@ -2917,10 +2924,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C32">
         <v>-14.47091</v>
@@ -2929,25 +2936,25 @@
         <v>132.2283</v>
       </c>
       <c r="N32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R32" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S32">
         <v>463.72768</v>
       </c>
       <c r="U32" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AD32">
         <v>9</v>
@@ -2955,10 +2962,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33">
         <v>-14.477963</v>
@@ -2967,25 +2974,25 @@
         <v>132.457248</v>
       </c>
       <c r="N33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R33" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="S33">
         <v>366.1008000000001</v>
       </c>
       <c r="U33" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AD33">
         <v>9</v>
@@ -2993,10 +3000,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C34">
         <v>-14.38877</v>
@@ -3005,25 +3012,25 @@
         <v>132.148</v>
       </c>
       <c r="N34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O34" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R34" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S34">
         <v>475.93104</v>
       </c>
       <c r="U34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AD34">
         <v>9</v>
@@ -3031,10 +3038,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C35">
         <v>-14.38877</v>
@@ -3043,25 +3050,25 @@
         <v>132.148</v>
       </c>
       <c r="N35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O35" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R35" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S35">
         <v>402.71088</v>
       </c>
       <c r="U35" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD35">
         <v>9</v>
@@ -3069,10 +3076,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C36">
         <v>-14.47217</v>
@@ -3081,25 +3088,25 @@
         <v>132.2196</v>
       </c>
       <c r="N36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R36" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S36">
         <v>427.1176</v>
       </c>
       <c r="U36" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AD36">
         <v>9</v>
@@ -3107,10 +3114,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C37">
         <v>-14.45491</v>
@@ -3119,22 +3126,22 @@
         <v>132.2581</v>
       </c>
       <c r="N37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="U37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AD37">
         <v>9</v>
@@ -3142,10 +3149,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C38">
         <v>-14.51583</v>
@@ -3154,25 +3161,25 @@
         <v>132.4334</v>
       </c>
       <c r="N38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R38" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S38">
         <v>427.1176</v>
       </c>
       <c r="U38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AD38">
         <v>9</v>
@@ -3180,10 +3187,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C39">
         <v>-14.48099</v>
@@ -3192,25 +3199,25 @@
         <v>132.2252</v>
       </c>
       <c r="N39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R39" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S39">
         <v>469.8293600000001</v>
       </c>
       <c r="U39" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AD39">
         <v>9</v>
@@ -3218,10 +3225,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C40">
         <v>-14.46388</v>
@@ -3230,25 +3237,25 @@
         <v>132.2605</v>
       </c>
       <c r="N40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q40" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="R40" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S40">
         <v>463.72768</v>
       </c>
       <c r="U40" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AD40">
         <v>9</v>
@@ -3256,10 +3263,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C41">
         <v>-14.6484038311049</v>
@@ -3268,25 +3275,25 @@
         <v>132.013681706129</v>
       </c>
       <c r="N41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q41" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="R41" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="S41">
         <v>433.21928</v>
       </c>
       <c r="U41" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AD41">
         <v>9</v>
@@ -3294,10 +3301,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C42">
         <v>-14.5597609146966</v>
@@ -3306,25 +3313,25 @@
         <v>131.974755158304</v>
       </c>
       <c r="N42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q42" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R42" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="S42">
         <v>433.21928</v>
       </c>
       <c r="U42" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AD42">
         <v>9</v>
@@ -3332,10 +3339,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43">
         <v>-14.43828</v>
@@ -3344,25 +3351,25 @@
         <v>132.226</v>
       </c>
       <c r="N43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O43" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q43" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="R43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="S43">
         <v>482.03272</v>
       </c>
       <c r="U43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD43">
         <v>9</v>
@@ -3370,10 +3377,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44">
         <v>-14.48024</v>
@@ -3382,25 +3389,25 @@
         <v>132.2559</v>
       </c>
       <c r="N44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q44" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="R44" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S44">
         <v>445.42264</v>
       </c>
       <c r="U44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AD44">
         <v>9</v>
@@ -3408,10 +3415,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45">
         <v>-14.47885</v>
@@ -3420,25 +3427,25 @@
         <v>132.2347</v>
       </c>
       <c r="N45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P45" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R45" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="S45">
         <v>421.0159200000001</v>
       </c>
       <c r="U45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AD45">
         <v>9</v>
@@ -3446,10 +3453,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C46">
         <v>-14.46072</v>
@@ -3458,25 +3465,25 @@
         <v>132.3954</v>
       </c>
       <c r="N46" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O46" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R46" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S46">
         <v>555.25288</v>
       </c>
       <c r="U46" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD46">
         <v>9</v>
@@ -3484,10 +3491,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C47">
         <v>-14.37364</v>
@@ -3496,25 +3503,25 @@
         <v>132.1554</v>
       </c>
       <c r="N47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O47" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P47" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q47" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="R47" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S47">
         <v>488.1344</v>
       </c>
       <c r="U47" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AD47">
         <v>9</v>
@@ -3522,10 +3529,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C48">
         <v>-14.6052</v>
@@ -3534,25 +3541,25 @@
         <v>132.4477</v>
       </c>
       <c r="N48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q48" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R48" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S48">
         <v>439.32096</v>
       </c>
       <c r="U48" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AD48">
         <v>9</v>
@@ -3560,10 +3567,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C49">
         <v>-14.49207</v>
@@ -3572,25 +3579,25 @@
         <v>132.331</v>
       </c>
       <c r="N49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O49" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P49" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q49" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R49" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S49">
         <v>500.33776</v>
       </c>
       <c r="U49" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AD49">
         <v>9</v>
@@ -3598,10 +3605,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C50">
         <v>-14.41238</v>
@@ -3610,25 +3617,25 @@
         <v>132.1743</v>
       </c>
       <c r="N50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R50" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S50">
         <v>482.03272</v>
       </c>
       <c r="U50" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AD50">
         <v>9</v>
@@ -3636,10 +3643,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C51">
         <v>-14.449762341958</v>
@@ -3648,25 +3655,25 @@
         <v>131.688069705176</v>
       </c>
       <c r="N51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R51" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S51">
         <v>384.40584</v>
       </c>
       <c r="U51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AD51">
         <v>9</v>
@@ -3674,10 +3681,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C52">
         <v>-14.57862</v>
@@ -3686,25 +3693,25 @@
         <v>132.5077</v>
       </c>
       <c r="N52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O52" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q52" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R52" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S52">
         <v>414.91424</v>
       </c>
       <c r="U52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD52">
         <v>9</v>
@@ -3712,10 +3719,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C53">
         <v>-14.42845</v>
@@ -3724,25 +3731,25 @@
         <v>132.2083</v>
       </c>
       <c r="N53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q53" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="R53" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S53">
         <v>414.91424</v>
       </c>
       <c r="U53" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AD53">
         <v>9</v>
@@ -3750,10 +3757,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C54">
         <v>-14.462216</v>
@@ -3762,25 +3769,25 @@
         <v>132.310862</v>
       </c>
       <c r="N54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P54" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q54" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R54" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S54">
         <v>451.5243200000001</v>
       </c>
       <c r="U54" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD54">
         <v>9</v>
@@ -3788,10 +3795,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C55">
         <v>-14.5049570813794</v>
@@ -3800,25 +3807,25 @@
         <v>131.71128322119</v>
       </c>
       <c r="N55" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P55" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q55" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R55" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S55">
         <v>280.67728</v>
       </c>
       <c r="U55" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AD55">
         <v>9</v>
@@ -3826,10 +3833,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C56">
         <v>-14.53955</v>
@@ -3838,25 +3845,25 @@
         <v>132.4678</v>
       </c>
       <c r="N56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P56" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q56" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R56" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S56">
         <v>329.4907200000001</v>
       </c>
       <c r="U56" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AD56">
         <v>9</v>
@@ -3864,10 +3871,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C57">
         <v>-14.61845</v>
@@ -3876,25 +3883,25 @@
         <v>132.2018</v>
       </c>
       <c r="N57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O57" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P57" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="R57" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S57">
         <v>384.40584</v>
       </c>
       <c r="U57" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AD57">
         <v>9</v>
@@ -3902,10 +3909,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C58">
         <v>-15.601</v>
@@ -3914,25 +3921,25 @@
         <v>133.1775</v>
       </c>
       <c r="N58" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O58" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P58" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="R58" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S58">
         <v>732.2016000000001</v>
       </c>
       <c r="U58" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD58">
         <v>9</v>
@@ -3940,10 +3947,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C59">
         <v>-16.4246274084702</v>
@@ -3952,25 +3959,25 @@
         <v>134.602017398501</v>
       </c>
       <c r="N59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O59" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P59" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q59" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="R59" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="S59">
         <v>518.6428000000001</v>
       </c>
       <c r="U59" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AD59">
         <v>9</v>
@@ -3978,10 +3985,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C60">
         <v>-16.3854521742903</v>
@@ -3990,25 +3997,25 @@
         <v>134.633512797705</v>
       </c>
       <c r="N60" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O60" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q60" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R60" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="S60">
         <v>585.7612800000001</v>
       </c>
       <c r="U60" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AD60">
         <v>9</v>
@@ -4016,10 +4023,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C61">
         <v>-16.3274</v>
@@ -4028,25 +4035,25 @@
         <v>134.7119</v>
       </c>
       <c r="N61" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O61" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R61" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S61">
         <v>854.2352000000001</v>
       </c>
       <c r="U61" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AD61">
         <v>9</v>
@@ -4054,10 +4061,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C62">
         <v>-16.4856</v>
@@ -4066,25 +4073,25 @@
         <v>134.7261</v>
       </c>
       <c r="N62" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O62" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P62" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q62" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R62" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S62">
         <v>591.86296</v>
       </c>
       <c r="U62" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AD62">
         <v>9</v>
@@ -4092,10 +4099,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C63">
         <v>-16.9257</v>
@@ -4104,25 +4111,25 @@
         <v>134.7913</v>
       </c>
       <c r="N63" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O63" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="R63" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="S63">
         <v>506.4394400000001</v>
       </c>
       <c r="U63" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AD63">
         <v>9</v>
@@ -4130,10 +4137,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C64">
         <v>-16.5969</v>
@@ -4142,25 +4149,25 @@
         <v>134.8011</v>
       </c>
       <c r="N64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O64" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q64" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R64" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="S64">
         <v>567.4562400000001</v>
       </c>
       <c r="U64" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AD64">
         <v>9</v>
@@ -4168,10 +4175,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C65">
         <v>-16.3997</v>
@@ -4180,25 +4187,25 @@
         <v>134.7048</v>
       </c>
       <c r="N65" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P65" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q65" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="R65" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="S65">
         <v>579.6596000000001</v>
       </c>
       <c r="U65" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AD65">
         <v>9</v>
@@ -4206,10 +4213,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C66">
         <v>-16.4561883563999</v>
@@ -4218,25 +4225,25 @@
         <v>134.648044388353</v>
       </c>
       <c r="N66" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O66" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P66" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q66" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="S66">
         <v>585.7612800000001</v>
       </c>
       <c r="U66" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AD66">
         <v>9</v>
@@ -4244,10 +4251,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C67">
         <v>-16.48</v>
@@ -4256,25 +4263,25 @@
         <v>133.9798</v>
       </c>
       <c r="N67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P67" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R67" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="S67">
         <v>536.94784</v>
       </c>
       <c r="U67" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AD67">
         <v>9</v>
@@ -4282,10 +4289,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C68">
         <v>-16.3464763323004</v>
@@ -4294,25 +4301,25 @@
         <v>133.884561881875</v>
       </c>
       <c r="N68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O68" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P68" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q68" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R68" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S68">
         <v>396.6092</v>
       </c>
       <c r="U68" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AD68">
         <v>9</v>
@@ -4320,10 +4327,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C69">
         <v>-16.619857486</v>
@@ -4332,25 +4339,25 @@
         <v>133.578681781</v>
       </c>
       <c r="N69" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P69" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q69" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R69" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S69">
         <v>567.4562400000001</v>
       </c>
       <c r="U69" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AD69">
         <v>9</v>
@@ -4358,10 +4365,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C70">
         <v>-16.5485</v>
@@ -4370,25 +4377,25 @@
         <v>133.7701</v>
       </c>
       <c r="N70" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P70" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q70" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R70" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="S70">
         <v>597.96464</v>
       </c>
       <c r="U70" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AD70">
         <v>9</v>
@@ -4396,10 +4403,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C71">
         <v>-17.0648</v>
@@ -4408,25 +4415,25 @@
         <v>133.41</v>
       </c>
       <c r="N71" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P71" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q71" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R71" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S71">
         <v>610.168</v>
       </c>
       <c r="U71" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AD71">
         <v>9</v>
@@ -4434,10 +4441,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C72">
         <v>-18.323</v>
@@ -4446,25 +4453,25 @@
         <v>133.8874</v>
       </c>
       <c r="N72" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O72" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P72" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q72" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R72" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="S72">
         <v>610.168</v>
       </c>
       <c r="U72" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AD72">
         <v>9</v>
@@ -4472,10 +4479,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C73">
         <v>-18.0408</v>
@@ -4484,25 +4491,25 @@
         <v>134.3971</v>
       </c>
       <c r="N73" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O73" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P73" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q73" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R73" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S73">
         <v>591.86296</v>
       </c>
       <c r="U73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD73">
         <v>9</v>
@@ -4510,10 +4517,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C74">
         <v>-17.7401</v>
@@ -4522,25 +4529,25 @@
         <v>133.724909</v>
       </c>
       <c r="N74" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O74" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P74" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q74" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R74" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S74">
         <v>396.6092</v>
       </c>
       <c r="U74" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AD74">
         <v>9</v>
@@ -4548,10 +4555,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C75">
         <v>-15.271023</v>
@@ -4560,25 +4567,25 @@
         <v>133.125561</v>
       </c>
       <c r="N75" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O75" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P75" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q75" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="R75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="S75">
         <v>732.2016000000001</v>
       </c>
       <c r="U75" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AD75">
         <v>9</v>
@@ -4586,10 +4593,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C76">
         <v>-15.3733385942091</v>
@@ -4598,25 +4605,25 @@
         <v>133.16522788068</v>
       </c>
       <c r="N76" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P76" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q76" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R76" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S76">
         <v>732.2016000000001</v>
       </c>
       <c r="U76" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AD76">
         <v>9</v>
@@ -4624,10 +4631,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C77">
         <v>-15.5927</v>
@@ -4636,25 +4643,25 @@
         <v>133.2249</v>
       </c>
       <c r="N77" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O77" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P77" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q77" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="R77" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S77">
         <v>732.2016000000001</v>
       </c>
       <c r="U77" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AD77">
         <v>9</v>
@@ -4662,10 +4669,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C78">
         <v>-15.86713284</v>
@@ -4674,25 +4681,25 @@
         <v>133.4067349</v>
       </c>
       <c r="N78" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O78" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P78" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q78" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R78" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="S78">
         <v>793.2184000000001</v>
       </c>
       <c r="U78" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AD78">
         <v>9</v>
@@ -4700,10 +4707,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C79">
         <v>-16.3464763323004</v>
@@ -4712,25 +4719,25 @@
         <v>133.884561881875</v>
       </c>
       <c r="N79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O79" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P79" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q79" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R79" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S79">
         <v>396.6092</v>
       </c>
       <c r="U79" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AD79">
         <v>9</v>
@@ -4738,10 +4745,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C80">
         <v>-16.308779</v>
@@ -4750,25 +4757,25 @@
         <v>133.385114</v>
       </c>
       <c r="N80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O80" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P80" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q80" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="R80" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S80">
         <v>726.0999200000001</v>
       </c>
       <c r="U80" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD80">
         <v>9</v>
@@ -4776,10 +4783,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C81">
         <v>-16.43265831</v>
@@ -4788,25 +4795,25 @@
         <v>134.5835343</v>
       </c>
       <c r="N81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O81" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P81" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q81" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R81" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="S81">
         <v>543.04952</v>
       </c>
       <c r="U81" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AD81">
         <v>9</v>
@@ -4814,10 +4821,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C82">
         <v>-16.38771649</v>
@@ -4826,25 +4833,25 @@
         <v>134.7943708</v>
       </c>
       <c r="N82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O82" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P82" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q82" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R82" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="S82">
         <v>604.06632</v>
       </c>
       <c r="U82" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AD82">
         <v>9</v>
@@ -4852,7 +4859,7 @@
     </row>
     <row r="83" spans="1:30">
       <c r="B83" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C83">
         <v>-14.933136</v>
@@ -4861,25 +4868,25 @@
         <v>133.134522</v>
       </c>
       <c r="N83" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P83" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q83" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R83" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S83">
         <v>1037.2856</v>
       </c>
       <c r="U83" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AD83">
         <v>9</v>
@@ -4887,7 +4894,7 @@
     </row>
     <row r="84" spans="1:30">
       <c r="B84" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C84">
         <v>-14.933136</v>
@@ -4896,25 +4903,25 @@
         <v>133.134522</v>
       </c>
       <c r="N84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O84" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P84" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q84" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R84" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S84">
         <v>976.2688000000001</v>
       </c>
       <c r="U84" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AD84">
         <v>9</v>
@@ -4922,7 +4929,7 @@
     </row>
     <row r="85" spans="1:30">
       <c r="B85" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C85">
         <v>-14.933136</v>
@@ -4931,25 +4938,25 @@
         <v>133.134522</v>
       </c>
       <c r="N85" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P85" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R85" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="S85">
         <v>1098.3024</v>
       </c>
       <c r="U85" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AD85">
         <v>9</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/AUSTRALIA-MATARANKA_Datenbank/before_conversion_australia_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/AUSTRALIA-MATARANKA_Datenbank/before_conversion_australia_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="427">
   <si>
     <t>location</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Botany Walk Spring</t>
+  </si>
+  <si>
+    <t>Limestone</t>
   </si>
   <si>
     <t>7</t>
@@ -1795,26 +1798,29 @@
       <c r="D2">
         <v>132.285449884</v>
       </c>
+      <c r="F2" t="s">
+        <v>111</v>
+      </c>
       <c r="N2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S2">
         <v>524.74448</v>
       </c>
       <c r="U2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AD2">
         <v>9</v>
@@ -1833,26 +1839,29 @@
       <c r="D3">
         <v>132.395</v>
       </c>
+      <c r="F3" t="s">
+        <v>111</v>
+      </c>
       <c r="N3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S3">
         <v>445.42264</v>
       </c>
       <c r="U3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AD3">
         <v>9</v>
@@ -1871,26 +1880,29 @@
       <c r="D4">
         <v>132.059519</v>
       </c>
+      <c r="F4" t="s">
+        <v>111</v>
+      </c>
       <c r="N4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S4">
         <v>402.71088</v>
       </c>
       <c r="U4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AD4">
         <v>9</v>
@@ -1909,26 +1921,29 @@
       <c r="D5">
         <v>132.059519</v>
       </c>
+      <c r="F5" t="s">
+        <v>111</v>
+      </c>
       <c r="N5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S5">
         <v>341.69408</v>
       </c>
       <c r="U5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AD5">
         <v>9</v>
@@ -1947,26 +1962,29 @@
       <c r="D6">
         <v>132.4713</v>
       </c>
+      <c r="F6" t="s">
+        <v>111</v>
+      </c>
       <c r="N6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="S6">
         <v>512.5411200000001</v>
       </c>
       <c r="U6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AD6">
         <v>9</v>
@@ -1985,26 +2003,29 @@
       <c r="D7">
         <v>132.247</v>
       </c>
+      <c r="F7" t="s">
+        <v>111</v>
+      </c>
       <c r="N7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S7">
         <v>482.03272</v>
       </c>
       <c r="U7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD7">
         <v>9</v>
@@ -2023,26 +2044,29 @@
       <c r="D8">
         <v>132.2414534</v>
       </c>
+      <c r="F8" t="s">
+        <v>111</v>
+      </c>
       <c r="N8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S8">
         <v>366.1008000000001</v>
       </c>
       <c r="U8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AD8">
         <v>9</v>
@@ -2061,26 +2085,29 @@
       <c r="D9">
         <v>132.5053</v>
       </c>
+      <c r="F9" t="s">
+        <v>111</v>
+      </c>
       <c r="N9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="R9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S9">
         <v>408.81256</v>
       </c>
       <c r="U9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AD9">
         <v>9</v>
@@ -2099,26 +2126,29 @@
       <c r="D10">
         <v>132.213009476</v>
       </c>
+      <c r="F10" t="s">
+        <v>111</v>
+      </c>
       <c r="N10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="S10">
         <v>421.0159200000001</v>
       </c>
       <c r="U10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AD10">
         <v>9</v>
@@ -2137,26 +2167,29 @@
       <c r="D11">
         <v>132.2043</v>
       </c>
+      <c r="F11" t="s">
+        <v>111</v>
+      </c>
       <c r="N11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S11">
         <v>366.1008000000001</v>
       </c>
       <c r="U11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD11">
         <v>9</v>
@@ -2175,26 +2208,29 @@
       <c r="D12">
         <v>132.295794198</v>
       </c>
+      <c r="F12" t="s">
+        <v>111</v>
+      </c>
       <c r="N12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="R12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S12">
         <v>463.72768</v>
       </c>
       <c r="U12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AD12">
         <v>9</v>
@@ -2213,26 +2249,29 @@
       <c r="D13">
         <v>132.295794198</v>
       </c>
+      <c r="F13" t="s">
+        <v>111</v>
+      </c>
       <c r="N13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S13">
         <v>421.0159200000001</v>
       </c>
       <c r="U13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD13">
         <v>9</v>
@@ -2251,26 +2290,29 @@
       <c r="D14">
         <v>132.255447</v>
       </c>
+      <c r="F14" t="s">
+        <v>111</v>
+      </c>
       <c r="N14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="S14">
         <v>402.71088</v>
       </c>
       <c r="U14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD14">
         <v>9</v>
@@ -2289,26 +2331,29 @@
       <c r="D15">
         <v>132.150887</v>
       </c>
+      <c r="F15" t="s">
+        <v>111</v>
+      </c>
       <c r="N15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S15">
         <v>482.03272</v>
       </c>
       <c r="U15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AD15">
         <v>9</v>
@@ -2327,26 +2372,29 @@
       <c r="D16">
         <v>132.2691</v>
       </c>
+      <c r="F16" t="s">
+        <v>111</v>
+      </c>
       <c r="N16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="R16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="S16">
         <v>286.77896</v>
       </c>
       <c r="U16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD16">
         <v>9</v>
@@ -2365,26 +2413,29 @@
       <c r="D17">
         <v>132.2564</v>
       </c>
+      <c r="F17" t="s">
+        <v>111</v>
+      </c>
       <c r="N17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="R17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S17">
         <v>451.5243200000001</v>
       </c>
       <c r="U17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AD17">
         <v>9</v>
@@ -2403,26 +2454,29 @@
       <c r="D18">
         <v>132.235</v>
       </c>
+      <c r="F18" t="s">
+        <v>111</v>
+      </c>
       <c r="N18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S18">
         <v>408.81256</v>
       </c>
       <c r="U18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD18">
         <v>9</v>
@@ -2441,26 +2495,29 @@
       <c r="D19">
         <v>132.2368</v>
       </c>
+      <c r="F19" t="s">
+        <v>111</v>
+      </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="R19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S19">
         <v>408.81256</v>
       </c>
       <c r="U19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD19">
         <v>9</v>
@@ -2479,26 +2536,29 @@
       <c r="D20">
         <v>132.2492</v>
       </c>
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
       <c r="N20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S20">
         <v>451.5243200000001</v>
       </c>
       <c r="U20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AD20">
         <v>9</v>
@@ -2517,26 +2577,29 @@
       <c r="D21">
         <v>132.261</v>
       </c>
+      <c r="F21" t="s">
+        <v>111</v>
+      </c>
       <c r="N21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q21" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="R21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S21">
         <v>585.7612800000001</v>
       </c>
       <c r="U21" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AD21">
         <v>9</v>
@@ -2555,26 +2618,29 @@
       <c r="D22">
         <v>132.2505</v>
       </c>
+      <c r="F22" t="s">
+        <v>111</v>
+      </c>
       <c r="N22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R22" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S22">
         <v>463.72768</v>
       </c>
       <c r="U22" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD22">
         <v>9</v>
@@ -2593,26 +2659,29 @@
       <c r="D23">
         <v>132.2504</v>
       </c>
+      <c r="F23" t="s">
+        <v>111</v>
+      </c>
       <c r="N23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O23" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R23" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S23">
         <v>500.33776</v>
       </c>
       <c r="U23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AD23">
         <v>9</v>
@@ -2631,26 +2700,29 @@
       <c r="D24">
         <v>132.2453</v>
       </c>
+      <c r="F24" t="s">
+        <v>111</v>
+      </c>
       <c r="N24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R24" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="S24">
         <v>451.5243200000001</v>
       </c>
       <c r="U24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AD24">
         <v>9</v>
@@ -2669,26 +2741,29 @@
       <c r="D25">
         <v>132.2365</v>
       </c>
+      <c r="F25" t="s">
+        <v>111</v>
+      </c>
       <c r="N25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q25" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R25" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="S25">
         <v>378.30416</v>
       </c>
       <c r="U25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD25">
         <v>9</v>
@@ -2707,26 +2782,29 @@
       <c r="D26">
         <v>132.2401</v>
       </c>
+      <c r="F26" t="s">
+        <v>111</v>
+      </c>
       <c r="N26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q26" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R26" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S26">
         <v>482.03272</v>
       </c>
       <c r="U26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD26">
         <v>9</v>
@@ -2745,26 +2823,29 @@
       <c r="D27">
         <v>132.2837</v>
       </c>
+      <c r="F27" t="s">
+        <v>111</v>
+      </c>
       <c r="N27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O27" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q27" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R27" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S27">
         <v>488.1344</v>
       </c>
       <c r="U27" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AD27">
         <v>9</v>
@@ -2783,26 +2864,29 @@
       <c r="D28">
         <v>132.2358</v>
       </c>
+      <c r="F28" t="s">
+        <v>111</v>
+      </c>
       <c r="N28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R28" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S28">
         <v>457.626</v>
       </c>
       <c r="U28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD28">
         <v>9</v>
@@ -2821,26 +2905,29 @@
       <c r="D29">
         <v>132.284</v>
       </c>
+      <c r="F29" t="s">
+        <v>111</v>
+      </c>
       <c r="N29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q29" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S29">
         <v>414.91424</v>
       </c>
       <c r="U29" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AD29">
         <v>9</v>
@@ -2859,26 +2946,29 @@
       <c r="D30">
         <v>132.174356</v>
       </c>
+      <c r="F30" t="s">
+        <v>111</v>
+      </c>
       <c r="N30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R30" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S30">
         <v>335.5924</v>
       </c>
       <c r="U30" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AD30">
         <v>9</v>
@@ -2897,26 +2987,29 @@
       <c r="D31">
         <v>132.1967</v>
       </c>
+      <c r="F31" t="s">
+        <v>111</v>
+      </c>
       <c r="N31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R31" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S31">
         <v>390.5075200000001</v>
       </c>
       <c r="U31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AD31">
         <v>9</v>
@@ -2935,26 +3028,29 @@
       <c r="D32">
         <v>132.2283</v>
       </c>
+      <c r="F32" t="s">
+        <v>111</v>
+      </c>
       <c r="N32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R32" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S32">
         <v>463.72768</v>
       </c>
       <c r="U32" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD32">
         <v>9</v>
@@ -2973,26 +3069,29 @@
       <c r="D33">
         <v>132.457248</v>
       </c>
+      <c r="F33" t="s">
+        <v>111</v>
+      </c>
       <c r="N33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O33" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q33" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R33" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S33">
         <v>366.1008000000001</v>
       </c>
       <c r="U33" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AD33">
         <v>9</v>
@@ -3011,26 +3110,29 @@
       <c r="D34">
         <v>132.148</v>
       </c>
+      <c r="F34" t="s">
+        <v>111</v>
+      </c>
       <c r="N34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R34" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="S34">
         <v>475.93104</v>
       </c>
       <c r="U34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AD34">
         <v>9</v>
@@ -3049,26 +3151,29 @@
       <c r="D35">
         <v>132.148</v>
       </c>
+      <c r="F35" t="s">
+        <v>111</v>
+      </c>
       <c r="N35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O35" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q35" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R35" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S35">
         <v>402.71088</v>
       </c>
       <c r="U35" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AD35">
         <v>9</v>
@@ -3087,26 +3192,29 @@
       <c r="D36">
         <v>132.2196</v>
       </c>
+      <c r="F36" t="s">
+        <v>111</v>
+      </c>
       <c r="N36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R36" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S36">
         <v>427.1176</v>
       </c>
       <c r="U36" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AD36">
         <v>9</v>
@@ -3125,23 +3233,26 @@
       <c r="D37">
         <v>132.2581</v>
       </c>
+      <c r="F37" t="s">
+        <v>111</v>
+      </c>
       <c r="N37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD37">
         <v>9</v>
@@ -3160,26 +3271,29 @@
       <c r="D38">
         <v>132.4334</v>
       </c>
+      <c r="F38" t="s">
+        <v>111</v>
+      </c>
       <c r="N38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q38" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="R38" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S38">
         <v>427.1176</v>
       </c>
       <c r="U38" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AD38">
         <v>9</v>
@@ -3198,26 +3312,29 @@
       <c r="D39">
         <v>132.2252</v>
       </c>
+      <c r="F39" t="s">
+        <v>111</v>
+      </c>
       <c r="N39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O39" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S39">
         <v>469.8293600000001</v>
       </c>
       <c r="U39" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD39">
         <v>9</v>
@@ -3236,26 +3353,29 @@
       <c r="D40">
         <v>132.2605</v>
       </c>
+      <c r="F40" t="s">
+        <v>111</v>
+      </c>
       <c r="N40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P40" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="R40" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S40">
         <v>463.72768</v>
       </c>
       <c r="U40" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AD40">
         <v>9</v>
@@ -3274,26 +3394,29 @@
       <c r="D41">
         <v>132.013681706129</v>
       </c>
+      <c r="F41" t="s">
+        <v>111</v>
+      </c>
       <c r="N41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q41" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R41" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="S41">
         <v>433.21928</v>
       </c>
       <c r="U41" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AD41">
         <v>9</v>
@@ -3312,26 +3435,29 @@
       <c r="D42">
         <v>131.974755158304</v>
       </c>
+      <c r="F42" t="s">
+        <v>111</v>
+      </c>
       <c r="N42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P42" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q42" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="R42" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="S42">
         <v>433.21928</v>
       </c>
       <c r="U42" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AD42">
         <v>9</v>
@@ -3350,26 +3476,29 @@
       <c r="D43">
         <v>132.226</v>
       </c>
+      <c r="F43" t="s">
+        <v>111</v>
+      </c>
       <c r="N43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O43" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q43" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R43" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="S43">
         <v>482.03272</v>
       </c>
       <c r="U43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD43">
         <v>9</v>
@@ -3388,26 +3517,29 @@
       <c r="D44">
         <v>132.2559</v>
       </c>
+      <c r="F44" t="s">
+        <v>111</v>
+      </c>
       <c r="N44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q44" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R44" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S44">
         <v>445.42264</v>
       </c>
       <c r="U44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD44">
         <v>9</v>
@@ -3426,26 +3558,29 @@
       <c r="D45">
         <v>132.2347</v>
       </c>
+      <c r="F45" t="s">
+        <v>111</v>
+      </c>
       <c r="N45" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P45" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q45" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R45" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S45">
         <v>421.0159200000001</v>
       </c>
       <c r="U45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD45">
         <v>9</v>
@@ -3464,26 +3599,29 @@
       <c r="D46">
         <v>132.3954</v>
       </c>
+      <c r="F46" t="s">
+        <v>111</v>
+      </c>
       <c r="N46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O46" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R46" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S46">
         <v>555.25288</v>
       </c>
       <c r="U46" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AD46">
         <v>9</v>
@@ -3502,26 +3640,29 @@
       <c r="D47">
         <v>132.1554</v>
       </c>
+      <c r="F47" t="s">
+        <v>111</v>
+      </c>
       <c r="N47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O47" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q47" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R47" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S47">
         <v>488.1344</v>
       </c>
       <c r="U47" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AD47">
         <v>9</v>
@@ -3540,26 +3681,29 @@
       <c r="D48">
         <v>132.4477</v>
       </c>
+      <c r="F48" t="s">
+        <v>111</v>
+      </c>
       <c r="N48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q48" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R48" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S48">
         <v>439.32096</v>
       </c>
       <c r="U48" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AD48">
         <v>9</v>
@@ -3578,26 +3722,29 @@
       <c r="D49">
         <v>132.331</v>
       </c>
+      <c r="F49" t="s">
+        <v>111</v>
+      </c>
       <c r="N49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O49" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q49" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S49">
         <v>500.33776</v>
       </c>
       <c r="U49" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AD49">
         <v>9</v>
@@ -3616,26 +3763,29 @@
       <c r="D50">
         <v>132.1743</v>
       </c>
+      <c r="F50" t="s">
+        <v>111</v>
+      </c>
       <c r="N50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R50" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="S50">
         <v>482.03272</v>
       </c>
       <c r="U50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AD50">
         <v>9</v>
@@ -3654,26 +3804,29 @@
       <c r="D51">
         <v>131.688069705176</v>
       </c>
+      <c r="F51" t="s">
+        <v>111</v>
+      </c>
       <c r="N51" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O51" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="S51">
         <v>384.40584</v>
       </c>
       <c r="U51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AD51">
         <v>9</v>
@@ -3692,26 +3845,29 @@
       <c r="D52">
         <v>132.5077</v>
       </c>
+      <c r="F52" t="s">
+        <v>111</v>
+      </c>
       <c r="N52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O52" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q52" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R52" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S52">
         <v>414.91424</v>
       </c>
       <c r="U52" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD52">
         <v>9</v>
@@ -3730,26 +3886,29 @@
       <c r="D53">
         <v>132.2083</v>
       </c>
+      <c r="F53" t="s">
+        <v>111</v>
+      </c>
       <c r="N53" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q53" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="R53" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S53">
         <v>414.91424</v>
       </c>
       <c r="U53" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AD53">
         <v>9</v>
@@ -3768,26 +3927,29 @@
       <c r="D54">
         <v>132.310862</v>
       </c>
+      <c r="F54" t="s">
+        <v>111</v>
+      </c>
       <c r="N54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O54" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P54" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q54" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="R54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S54">
         <v>451.5243200000001</v>
       </c>
       <c r="U54" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AD54">
         <v>9</v>
@@ -3806,26 +3968,29 @@
       <c r="D55">
         <v>131.71128322119</v>
       </c>
+      <c r="F55" t="s">
+        <v>111</v>
+      </c>
       <c r="N55" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O55" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P55" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="R55" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S55">
         <v>280.67728</v>
       </c>
       <c r="U55" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AD55">
         <v>9</v>
@@ -3844,26 +4009,29 @@
       <c r="D56">
         <v>132.4678</v>
       </c>
+      <c r="F56" t="s">
+        <v>111</v>
+      </c>
       <c r="N56" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R56" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S56">
         <v>329.4907200000001</v>
       </c>
       <c r="U56" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AD56">
         <v>9</v>
@@ -3882,26 +4050,29 @@
       <c r="D57">
         <v>132.2018</v>
       </c>
+      <c r="F57" t="s">
+        <v>111</v>
+      </c>
       <c r="N57" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P57" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="S57">
         <v>384.40584</v>
       </c>
       <c r="U57" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AD57">
         <v>9</v>
@@ -3920,26 +4091,29 @@
       <c r="D58">
         <v>133.1775</v>
       </c>
+      <c r="F58" t="s">
+        <v>111</v>
+      </c>
       <c r="N58" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O58" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P58" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="R58" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S58">
         <v>732.2016000000001</v>
       </c>
       <c r="U58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AD58">
         <v>9</v>
@@ -3958,26 +4132,29 @@
       <c r="D59">
         <v>134.602017398501</v>
       </c>
+      <c r="F59" t="s">
+        <v>111</v>
+      </c>
       <c r="N59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P59" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q59" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R59" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S59">
         <v>518.6428000000001</v>
       </c>
       <c r="U59" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AD59">
         <v>9</v>
@@ -3996,26 +4173,29 @@
       <c r="D60">
         <v>134.633512797705</v>
       </c>
+      <c r="F60" t="s">
+        <v>111</v>
+      </c>
       <c r="N60" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O60" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P60" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q60" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R60" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S60">
         <v>585.7612800000001</v>
       </c>
       <c r="U60" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AD60">
         <v>9</v>
@@ -4034,26 +4214,29 @@
       <c r="D61">
         <v>134.7119</v>
       </c>
+      <c r="F61" t="s">
+        <v>111</v>
+      </c>
       <c r="N61" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O61" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q61" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R61" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="S61">
         <v>854.2352000000001</v>
       </c>
       <c r="U61" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AD61">
         <v>9</v>
@@ -4072,26 +4255,29 @@
       <c r="D62">
         <v>134.7261</v>
       </c>
+      <c r="F62" t="s">
+        <v>111</v>
+      </c>
       <c r="N62" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O62" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P62" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q62" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="R62" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="S62">
         <v>591.86296</v>
       </c>
       <c r="U62" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AD62">
         <v>9</v>
@@ -4110,26 +4296,29 @@
       <c r="D63">
         <v>134.7913</v>
       </c>
+      <c r="F63" t="s">
+        <v>111</v>
+      </c>
       <c r="N63" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O63" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="R63" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="S63">
         <v>506.4394400000001</v>
       </c>
       <c r="U63" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AD63">
         <v>9</v>
@@ -4148,26 +4337,29 @@
       <c r="D64">
         <v>134.8011</v>
       </c>
+      <c r="F64" t="s">
+        <v>111</v>
+      </c>
       <c r="N64" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O64" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P64" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q64" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R64" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="S64">
         <v>567.4562400000001</v>
       </c>
       <c r="U64" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AD64">
         <v>9</v>
@@ -4186,26 +4378,29 @@
       <c r="D65">
         <v>134.7048</v>
       </c>
+      <c r="F65" t="s">
+        <v>111</v>
+      </c>
       <c r="N65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P65" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q65" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R65" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="S65">
         <v>579.6596000000001</v>
       </c>
       <c r="U65" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AD65">
         <v>9</v>
@@ -4224,26 +4419,29 @@
       <c r="D66">
         <v>134.648044388353</v>
       </c>
+      <c r="F66" t="s">
+        <v>111</v>
+      </c>
       <c r="N66" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O66" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q66" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R66" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S66">
         <v>585.7612800000001</v>
       </c>
       <c r="U66" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AD66">
         <v>9</v>
@@ -4262,26 +4460,29 @@
       <c r="D67">
         <v>133.9798</v>
       </c>
+      <c r="F67" t="s">
+        <v>111</v>
+      </c>
       <c r="N67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R67" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S67">
         <v>536.94784</v>
       </c>
       <c r="U67" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AD67">
         <v>9</v>
@@ -4300,26 +4501,29 @@
       <c r="D68">
         <v>133.884561881875</v>
       </c>
+      <c r="F68" t="s">
+        <v>111</v>
+      </c>
       <c r="N68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O68" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P68" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q68" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R68" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S68">
         <v>396.6092</v>
       </c>
       <c r="U68" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AD68">
         <v>9</v>
@@ -4338,26 +4542,29 @@
       <c r="D69">
         <v>133.578681781</v>
       </c>
+      <c r="F69" t="s">
+        <v>111</v>
+      </c>
       <c r="N69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P69" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q69" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="R69" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S69">
         <v>567.4562400000001</v>
       </c>
       <c r="U69" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AD69">
         <v>9</v>
@@ -4376,26 +4583,29 @@
       <c r="D70">
         <v>133.7701</v>
       </c>
+      <c r="F70" t="s">
+        <v>111</v>
+      </c>
       <c r="N70" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P70" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q70" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R70" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S70">
         <v>597.96464</v>
       </c>
       <c r="U70" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AD70">
         <v>9</v>
@@ -4414,26 +4624,29 @@
       <c r="D71">
         <v>133.41</v>
       </c>
+      <c r="F71" t="s">
+        <v>111</v>
+      </c>
       <c r="N71" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P71" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q71" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R71" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="S71">
         <v>610.168</v>
       </c>
       <c r="U71" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AD71">
         <v>9</v>
@@ -4452,26 +4665,29 @@
       <c r="D72">
         <v>133.8874</v>
       </c>
+      <c r="F72" t="s">
+        <v>111</v>
+      </c>
       <c r="N72" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O72" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q72" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R72" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S72">
         <v>610.168</v>
       </c>
       <c r="U72" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AD72">
         <v>9</v>
@@ -4490,26 +4706,29 @@
       <c r="D73">
         <v>134.3971</v>
       </c>
+      <c r="F73" t="s">
+        <v>111</v>
+      </c>
       <c r="N73" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O73" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P73" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q73" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R73" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S73">
         <v>591.86296</v>
       </c>
       <c r="U73" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AD73">
         <v>9</v>
@@ -4528,26 +4747,29 @@
       <c r="D74">
         <v>133.724909</v>
       </c>
+      <c r="F74" t="s">
+        <v>111</v>
+      </c>
       <c r="N74" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O74" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P74" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q74" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="R74" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="S74">
         <v>396.6092</v>
       </c>
       <c r="U74" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AD74">
         <v>9</v>
@@ -4566,26 +4788,29 @@
       <c r="D75">
         <v>133.125561</v>
       </c>
+      <c r="F75" t="s">
+        <v>111</v>
+      </c>
       <c r="N75" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O75" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P75" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q75" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S75">
         <v>732.2016000000001</v>
       </c>
       <c r="U75" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AD75">
         <v>9</v>
@@ -4604,26 +4829,29 @@
       <c r="D76">
         <v>133.16522788068</v>
       </c>
+      <c r="F76" t="s">
+        <v>111</v>
+      </c>
       <c r="N76" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P76" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q76" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="R76" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S76">
         <v>732.2016000000001</v>
       </c>
       <c r="U76" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AD76">
         <v>9</v>
@@ -4642,26 +4870,29 @@
       <c r="D77">
         <v>133.2249</v>
       </c>
+      <c r="F77" t="s">
+        <v>111</v>
+      </c>
       <c r="N77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O77" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P77" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q77" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R77" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="S77">
         <v>732.2016000000001</v>
       </c>
       <c r="U77" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AD77">
         <v>9</v>
@@ -4680,26 +4911,29 @@
       <c r="D78">
         <v>133.4067349</v>
       </c>
+      <c r="F78" t="s">
+        <v>111</v>
+      </c>
       <c r="N78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O78" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P78" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q78" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="R78" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S78">
         <v>793.2184000000001</v>
       </c>
       <c r="U78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AD78">
         <v>9</v>
@@ -4718,26 +4952,29 @@
       <c r="D79">
         <v>133.884561881875</v>
       </c>
+      <c r="F79" t="s">
+        <v>111</v>
+      </c>
       <c r="N79" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P79" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q79" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R79" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S79">
         <v>396.6092</v>
       </c>
       <c r="U79" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AD79">
         <v>9</v>
@@ -4756,26 +4993,29 @@
       <c r="D80">
         <v>133.385114</v>
       </c>
+      <c r="F80" t="s">
+        <v>111</v>
+      </c>
       <c r="N80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O80" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P80" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q80" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R80" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="S80">
         <v>726.0999200000001</v>
       </c>
       <c r="U80" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD80">
         <v>9</v>
@@ -4794,26 +5034,29 @@
       <c r="D81">
         <v>134.5835343</v>
       </c>
+      <c r="F81" t="s">
+        <v>111</v>
+      </c>
       <c r="N81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P81" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q81" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R81" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S81">
         <v>543.04952</v>
       </c>
       <c r="U81" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AD81">
         <v>9</v>
@@ -4832,26 +5075,29 @@
       <c r="D82">
         <v>134.7943708</v>
       </c>
+      <c r="F82" t="s">
+        <v>111</v>
+      </c>
       <c r="N82" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O82" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q82" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R82" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S82">
         <v>604.06632</v>
       </c>
       <c r="U82" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AD82">
         <v>9</v>
@@ -4867,26 +5113,29 @@
       <c r="D83">
         <v>133.134522</v>
       </c>
+      <c r="F83" t="s">
+        <v>111</v>
+      </c>
       <c r="N83" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O83" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P83" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q83" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R83" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S83">
         <v>1037.2856</v>
       </c>
       <c r="U83" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AD83">
         <v>9</v>
@@ -4902,26 +5151,29 @@
       <c r="D84">
         <v>133.134522</v>
       </c>
+      <c r="F84" t="s">
+        <v>111</v>
+      </c>
       <c r="N84" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O84" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P84" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q84" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R84" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="S84">
         <v>976.2688000000001</v>
       </c>
       <c r="U84" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AD84">
         <v>9</v>
@@ -4937,26 +5189,29 @@
       <c r="D85">
         <v>133.134522</v>
       </c>
+      <c r="F85" t="s">
+        <v>111</v>
+      </c>
       <c r="N85" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O85" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P85" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q85" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="R85" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="S85">
         <v>1098.3024</v>
       </c>
       <c r="U85" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AD85">
         <v>9</v>
